--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0115.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0115.xlsx
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>*******</t>
+          <t>********</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>********</t>
+          <t>* * * * * * * *</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Nhiệm Vụ Thám Hiểm "Một Ngày Tuyệt Vời Để Bay Lượn"</t>
+          <t>Nhiệm Vụ Thám Hiểm "Ngày Hoàn Hảo Để Bay"</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Thử Thách Đua Xe Xây Dựng Tuyến Đường tại Silent Crag</t>
+          <t>Giải Đua Xây Dựng Tuyến Đường tại Vách Đá Vắng Lặng</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Tiếng Vang Từ Cuối Dải Ngân Hà</t>
+          <t>Tiếng Vọng Từ Cõi Hư Không</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Lời Hứa Giả Dối Cho Ngày Mai</t>
+          <t>Lời hứa hão huyền cho ngày mai</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Frostburn</t>
+          <t>Bỏng Sương</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Absolute Pulsation</t>
+          <t>Rung Động Tuyệt Đối</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Forged Dwarf Star</t>
+          <t>Ngôi Sao Lùn Đã Rèn</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Absolute Pulsation</t>
+          <t>Rung Động Tuyệt Đối</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Frostburn</t>
+          <t>Bỏng Sương</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Forged Dwarf Star</t>
+          <t>Ngôi Sao Lùn Đã Rèn</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Chương III - Đoạn Nối "Điều Ước Trong Tiếng Chuông"</t>
+          <t>Chương III - Chuyển Tiếp "Điều Ước Trong Chuông"</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Chương III Hồi V "Ánh Sao Từ Những Ngày Qua"</t>
+          <t>Chương III Hồi V "Ánh Sao Từ Ngày Xưa"</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Chương III - Đoạn Nối "Dưới Bầu Trời Đêm Tan Băng"</t>
+          <t>Chương III - Chuyển Tiếp "Dưới Bầu Trời Đêm Tan Băng"</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Ước Nguyện Trong Chuông</t>
+          <t>Điều Ước Trong Chuông</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Ánh Sao Từ Ngày Qua</t>
+          <t>Ánh Sao Ngày Xưa</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>New Region</t>
+          <t>Khu Vực Mới</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Roya Frostlands: The Dimmr Plains</t>
+          <t>Vùng Đất Băng Giá Roya: Đồng Bằng Dimmr</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Solisia Landing</t>
+          <t>Bãi Đáp Solisia</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Sealed Fissure</t>
+          <t>Khe Nứt Đã Niêm Phong</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Silent Crag</t>
+          <t>Vách Đá Im Lìm</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Dimmr Deep</t>
+          <t>Vực Sâu Mờ Mịt</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Roya Frostlands: The Dimmr Plains</t>
+          <t>Vùng Đất Băng Giá Roya: Đồng Bằng Dimmr</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Solisia Landing</t>
+          <t>Bãi Đáp Solisia</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Sealed Fissure</t>
+          <t>Khe Nứt Đã Niêm Phong</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Silent Crag</t>
+          <t>Vách Đá Im Lìm</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Dimmr Deep</t>
+          <t>Vực Sâu Mờ Mịt</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Nảy Bóng Sao</t>
+          <t>Vụ nổ sao</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Cubie Derby: Championship</t>
+          <t>Đua Cubie: Giải Vô Địch</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Lollo Express: Promise Delivered</t>
+          <t>Lollo Express: Lời Hứa Đã Thực Hiện</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Quà Tặng Của Lễ Kỷ Niệm Hoành Tráng</t>
+          <t>Mộng Đại Lễ</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Dimmr Traces</t>
+          <t>Dấu Vết Đồng Bằng Dimmr</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Dimmr Travelogue</t>
+          <t>Nhật Ký Hành Trình Dimmr</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Vực Sâu Ảo Ảnh: Giấc Mộng Sắc Màu</t>
+          <t>Tổ Tacet Ảo Ảnh: Giấc Mộng Sắc Màu</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Đến Vùng Đất Nghịch Lý</t>
+          <t>Vào Vùng Đất Nghịch Lý</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Vượt Sóng: Lãnh Địa Băng Giá Roya</t>
+          <t>Vượt Qua Những Con Sóng: Roya Frostlands</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Trở Lại Solaris</t>
+          <t>Trở lại Solaris</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Nảy Bóng Sao</t>
+          <t>Vụ nổ sao</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Cubie Derby: Championship</t>
+          <t>Đua Cubie: Giải Vô Địch</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Lollo Express: Promise Delivered</t>
+          <t>Lollo Express: Lời Hứa Đã Thực Hiện</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Quà Tặng Của Lễ Kỷ Niệm Hoành Tráng</t>
+          <t>Mộng Đại Lễ</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Dimmr Traces</t>
+          <t>Dấu Vết Đồng Bằng Dimmr</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Dimmr Travelogue</t>
+          <t>Nhật Ký Hành Trình Dimmr</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Vực Sâu Ảo Ảnh: Giấc Mộng Sắc Màu</t>
+          <t>Tổ Tacet Ảo Ảnh: Giấc Mộng Sắc Màu</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Đến Vùng Đất Nghịch Lý</t>
+          <t>Vào Vùng Đất Nghịch Lý</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Vượt Sóng: Lãnh Địa Băng Giá Roya</t>
+          <t>Vượt Qua Những Con Sóng: Roya Frostlands</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Second Coming of Solaris: Mùa Cộng Tác</t>
+          <t>Sự Trở Lại Của Solaris: Mùa Cộng Tác</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>New Outfits</t>
+          <t>Trang Phục Mới</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Vehicle Livery</t>
+          <t>Màu Sắc Phương Tiện</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>New WavesLine UI</t>
+          <t>Giao Diện Dòng Sóng Mới</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Nạp Lần Đầu 2x Lunite - Đặt lại</t>
+          <t>Mua gói Nạp Đầu Tiên 2x - Đặt lại Lunite</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Bountiful Waves</t>
+          <t>Sóng Dạt Dào</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Second Coming of Solaris: Mùa Cộng Tác</t>
+          <t>Sự Trở Lại Của Solaris: Mùa Cộng Tác</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>New Outfits</t>
+          <t>Trang Phục Mới</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Vehicle Livery</t>
+          <t>Màu Sắc Phương Tiện</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>New WavesLine UI</t>
+          <t>Giao Diện Dòng Sóng Mới</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Nạp Lần Đầu 2x Lunite - Đặt lại</t>
+          <t>Mua gói Nạp Đầu Tiên 2x - Đặt lại Lunite</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Bountiful Waves</t>
+          <t>Sóng Dạt Dào</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Resident Evil</t>
+          <t>Cư dân ác mộng</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Angry Birds</t>
+          <t>Những chú chim giận dữ</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Riders Republic</t>
+          <t>Cộng Hòa Kỵ Sĩ</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Lời Nguyện Ước Tuyết Yên Tĩnh</t>
+          <t>Wishes of Quiet Snowfall</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Cuộn Phim Ký Ức Đan Xen</t>
+          <t>Reel of Spliced Memories</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Sonata: Lời Nguyện Ước Tuyết Yên Tĩnh</t>
+          <t>Sonata: Lời Nguyện Tuyết Lặng</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Sonata: Cuộn Phim Ký Ức Đan Xen</t>
+          <t>Sonata: Cuộn Ký Ức Đan Xen</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Motorbike Aerial Tactics Mô-đun</t>
+          <t>Mô-đun Chiến Thuật Trên Không Xe Máy</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Aerial Tactics</t>
+          <t>Chiến Thuật Trên Không</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>UI Updates</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Trang sức</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Motorbike Aerial Tactics Mô-đun</t>
+          <t>Mô-đun Chiến Thuật Trên Không Xe Máy</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Aerial Tactics</t>
+          <t>Chiến Thuật Trên Không</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>UI Updates</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Trang sức</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Không có phần thưởng khả dụng để nhận</t>
+          <t>Không có phần thưởng nào để nhận</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Không nằm trong khoảng thời gian hợp lệ của nhiệm vụ</t>
+          <t>Ngoài khoảng thời gian hợp lệ của nhiệm vụ</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Reminiscence: Threnodian - Voidborne Construct</t>
+          <t>Hồi ức: Threnodian - Cỗ Máy Hư Không</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Blueprint</t>
+          <t>Bản Thiết Kế</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Send Rune 1</t>
+          <t>Gửi Rune 1</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Send Rune 2</t>
+          <t>Gửi Rune 2</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Send Rune 3</t>
+          <t>Gửi Rune 3</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Trạng thái thử thách đã cập nhật</t>
+          <t>Trạng thái thách đấu đã cập nhật</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Glacio Bite</t>
+          <t>Cắn Băng Giá</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
